--- a/AI Audit_Log_NguyenTuanManh.xlsx
+++ b/AI Audit_Log_NguyenTuanManh.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9108" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9708" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>STT</t>
   </si>
@@ -1240,19 +1240,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="165.6" spans="1:4">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI Audit_Log_NguyenTuanManh.xlsx
+++ b/AI Audit_Log_NguyenTuanManh.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9108" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week 1" sheetId="2" r:id="rId2"/>
     <sheet name="Week 2" sheetId="3" r:id="rId3"/>
     <sheet name="Week 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>STT</t>
   </si>
@@ -112,6 +113,38 @@
   <si>
     <t>Phản hồi: AI cung cấp 10 tiêu chí gồm: tính đầy đủ (completeness), nhất quán (consistency), khả thi (feasibility), có thể kiểm thử (testability), không mơ hồ (unambiguous), có thể truy vết (traceable), ưu tiên hóa (prioritized), chính xác (correct), độc lập với thiết kế (design-independent), và phù hợp chuẩn IEEE 830.
 Kiểm chứng: Danh sách AI đưa ra phù hợp với chuẩn IEEE 830 và tài liệu giảng viên cung cấp. Tuy nhiên, AI không đề cập đến tiêu chí "Verifiable" (có thể xác minh) vốn được tách riêng khỏi Testability trong một số tài liệu học thuật. Tôi đã bổ sung tiêu chí này vào checklist và dùng danh sách hoàn chỉnh để review SRS của nhóm — phát hiện 3 yêu cầu bị mơ hồ và 1 yêu cầu mâu thuẫn nhau.</t>
+  </si>
+  <si>
+    <t>Order Creation</t>
+  </si>
+  <si>
+    <t>Khi khách bấm đặt hàng trên Shopee, hệ thống tạo ra những dữ liệu gì? Giải thích trạng thái đầu tiên của đơn hàng là gì và tại sao cần có mã đơn hàng?</t>
+  </si>
+  <si>
+    <t>AI giải thích hệ thống tạo mã đơn, thông tin người nhận, địa chỉ và trạng thái Pending
+"Nếu thiếu mã đơn, điều gì xảy ra khi có 2 đơn cùng địa chỉ?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation &amp; Packing
+</t>
+  </si>
+  <si>
+    <t>Sau khi người bán xác nhận đơn, mã vận đơn (tracking number) được sinh ra như thế nào? QR Code và barcode khác nhau điểm gì trong logistics?</t>
+  </si>
+  <si>
+    <t>AI phân biệt QR Code chứa nhiều thông tin hơn barcode 1D, và trạng thái chuyển sang Ready To Ship → Packed
+"Tôi sẽ thiết kế màn hình in phiếu vận đơn dùng QR Code thay barcode"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickup &amp; First Hub
+</t>
+  </si>
+  <si>
+    <t>Khi shipper đến lấy hàng và quét barcode (SCAN #1), dữ liệu gì được ghi vào hệ thống? Sự kiện scan này khác gì so với GPS tracking?</t>
+  </si>
+  <si>
+    <t>AI giải thích đây là Scan Event Tracking, mỗi lần scan ghi timestamp + địa điểm, không phải GPS liên tục
+"Tracking của Shopee thực chất là chuỗi sự kiện rời rạc, không phải theo dõi thực tế"</t>
   </si>
 </sst>
 </file>
@@ -755,7 +788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -771,6 +804,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1136,7 +1172,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" ht="71.25" customHeight="1" spans="1:5">
       <c r="A2" s="2">
@@ -1342,4 +1378,77 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="50.2" customWidth="1"/>
+    <col min="3" max="3" width="40.7" customWidth="1"/>
+    <col min="4" max="4" width="53.4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="55.2" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="55.2" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit_Log_NguyenTuanManh.xlsx
+++ b/AI Audit_Log_NguyenTuanManh.xlsx
@@ -1,23 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="28788" windowHeight="12960" activeTab="7"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Template" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Week 1" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Week 2" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Week 3" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Week 4" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Week 5" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Week 6" sheetId="7" r:id="rId11"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="7" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="8" r:id="rId8"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="94">
   <si>
     <t>STT</t>
   </si>
@@ -304,50 +321,448 @@
     <t>AI liệt kê 4 nhóm: (1) Valid inputs → 201 Created, (2) Duplicate email → 409 Conflict, (3) Invalid email format → 400 Bad Request, (4) Missing required fields → 400 Bad Request. Mỗi nhóm có Return + Exception class + Log message mẫu.
 → Quyết định: Nhóm sử dụng toàn bộ gợi ý làm khung, sau đó điền giá trị cụ thể (email thật, password thật từ hệ thống FreshConnect). Thêm 1 UTCID cho Role=Logistics Dispatcher vì tính năng có 3 vai trò khác nhau.</t>
   </si>
+  <si>
+    <t>Xác định vai trò Logistics</t>
+  </si>
+  <si>
+    <t>"Logistics trong một sàn thương mại điện tử lớn như Shopee hay Taobao hoạt động như thế nào? Nó có phải chỉ là tính năng phụ không?"</t>
+  </si>
+  <si>
+    <t>AI khẳng định: logistics không phải tính năng phụ mà là hệ thống cốt lõi — giá trị sàn nằm ở việc hàng triệu đơn được di chuyển đúng nơi, đúng giờ, chi phí thấp nhất.
+Người học nhận ra: FreshConnect cần thiết kế logistics ngay từ đầu, không thể bổ sung sau.</t>
+  </si>
+  <si>
+    <t>State Machine – Trạng thái đơn hàng</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để quản lý trạng thái của một kiện hàng trong quá trình vận chuyển?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất nguyên tắc: mỗi kiện hàng chỉ có một trạng thái tại một thời điểm.
+Luồng: Đã tạo đơn → Xác nhận → Đang lấy → Đã lấy → Đến kho → Rời kho → Đang giao → Đã giao
+Người học quyết định: Thiết kế State Machine cho FreshConnect gồm bao nhiêu trạng thái? Có thêm trạng thái "Hoàn hàng" không?</t>
+  </si>
+  <si>
+    <t>Event-Driven – Chỉ scan khi có sự kiện</t>
+  </si>
+  <si>
+    <t>"Hệ thống có cần cập nhật vị trí liên tục khi xe đang chạy không?"</t>
+  </si>
+  <si>
+    <t>AI giải thích: không cập nhật liên tục — chỉ scan khi có sự kiện quan trọng (lấy hàng, đến kho, rời kho, giao hàng). Xe chạy 500km không ai quan tâm.
+Người học quyết định: Dùng kiến trúc Event-Driven cho FreshConnect: mỗi check-in tạo một TrackingEvent mới.</t>
+  </si>
+  <si>
+    <t>Scan QR – Thao tác kho tự động</t>
+  </si>
+  <si>
+    <t>"Nhân viên kho thao tác với hệ thống như thế nào để cập nhật trạng thái đơn hàng?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất: nhân viên chỉ quét QR, hệ thống tự nhận diện OrderID + WarehouseID + Time + Employee + Vehicle.
+Người học áp dụng: FreshConnect dùng QR trên kiện hàng, Driver/Warehouse staff quét = tạo TrackingEvent tự động, không cần nhập tay.</t>
+  </si>
+  <si>
+    <t>Container – Gom hàng theo lô</t>
+  </si>
+  <si>
+    <t>"Nếu có 1000 kiện hàng cùng tuyến đường, hệ thống xử lý như thế nào cho hiệu quả?"</t>
+  </si>
+  <si>
+    <t>AI giải thích mô hình Container: 1000 kiện → Container → Container lên xe. Xe chỉ scan container, 500 đơn cập nhật trạng thái đồng thời.
+Người học quyết định: FreshConnect có cần Container không? Với quy mô B2B nông sản thì nên gom theo lô Shipment hay Container?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -361,87 +776,560 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -631,24 +1519,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.88"/>
-    <col customWidth="1" min="2" max="2" width="26.88"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="45.0"/>
-    <col customWidth="1" min="5" max="26" width="9.0"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,61 +1549,61 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="9"/>
     </row>
-    <row r="2" ht="71.25" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="71.25" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="57.0" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="57" customHeight="1" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="71.25" customHeight="1">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="71.25" customHeight="1" spans="1:5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="85.5" customHeight="1">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="85.5" customHeight="1" spans="1:5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1715,28 +2603,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.88"/>
-    <col customWidth="1" min="2" max="2" width="26.88"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="45.0"/>
-    <col customWidth="1" min="5" max="26" width="9.0"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1750,31 +2636,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="99.75" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="99.75" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2776,28 +3662,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.88"/>
-    <col customWidth="1" min="2" max="2" width="26.88"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="45.0"/>
-    <col customWidth="1" min="5" max="26" width="9.0"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2811,17 +3695,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="99.75" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="99.75" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3824,28 +4708,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.88"/>
-    <col customWidth="1" min="2" max="2" width="26.88"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="45.0"/>
-    <col customWidth="1" min="5" max="26" width="9.0"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3859,17 +4741,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="99.75" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="99.75" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4872,28 +5754,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.75"/>
-    <col customWidth="1" min="2" max="2" width="59.25"/>
-    <col customWidth="1" min="3" max="3" width="46.63"/>
-    <col customWidth="1" min="4" max="4" width="62.0"/>
-    <col customWidth="1" min="5" max="26" width="8.75"/>
+    <col min="1" max="1" width="8.75" customWidth="1"/>
+    <col min="2" max="2" width="59.25" customWidth="1"/>
+    <col min="3" max="3" width="46.6333333333333" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="26" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4907,115 +5787,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="8" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="9" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6011,28 +6891,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.75"/>
-    <col customWidth="1" min="2" max="2" width="55.0"/>
-    <col customWidth="1" min="3" max="3" width="54.13"/>
-    <col customWidth="1" min="4" max="4" width="56.25"/>
-    <col customWidth="1" min="5" max="26" width="8.75"/>
+    <col min="1" max="1" width="8.75" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="54.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="56.25" customWidth="1"/>
+    <col min="5" max="26" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6046,115 +6924,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="8" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="9" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7150,28 +8028,28 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.88"/>
-    <col customWidth="1" min="2" max="2" width="26.88"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="45.0"/>
-    <col customWidth="1" min="5" max="26" width="9.0"/>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7185,31 +8063,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="148.5" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" ht="148.5" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="10" t="s">
+    <row r="3" ht="13.5" customHeight="1" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -8211,6 +9089,1104 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="82.8" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="110.4" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="8" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="9" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="10" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="11" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="12" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="13" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="14" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="15" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="16" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="17" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="18" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="19" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="20" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="21" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="22" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="23" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="24" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="25" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="26" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="27" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="28" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="29" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="30" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="31" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="32" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="33" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="34" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="35" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="36" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="37" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="38" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="39" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="40" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="41" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="42" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="43" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="44" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="45" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="46" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="47" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="48" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="49" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="50" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="51" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="52" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="53" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="54" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="55" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="56" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="57" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="58" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="59" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="60" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="61" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="62" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="63" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="64" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="65" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="66" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="67" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="68" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="69" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="70" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="71" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="72" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="73" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="74" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="75" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="76" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="77" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="78" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="79" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="80" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="81" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="82" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="83" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="84" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="85" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="86" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="87" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="88" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="89" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="90" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="91" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="92" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="93" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="94" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="95" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="96" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="97" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="98" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="99" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="100" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="101" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="102" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="103" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="104" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="105" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="106" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="107" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="108" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="109" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="110" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="111" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="112" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="113" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="114" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="115" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="116" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="117" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="118" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="119" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="120" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="121" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="122" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="123" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="124" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="125" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="126" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="127" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="128" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="129" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="130" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="131" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="132" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="133" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="134" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="135" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="136" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="137" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="138" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="139" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="140" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="141" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="142" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="143" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="144" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="145" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="146" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="147" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="148" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="149" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="150" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="151" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="152" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="153" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="154" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="155" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="156" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="157" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="158" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="159" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="160" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="161" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="162" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="163" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="164" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="165" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="166" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="167" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="168" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="169" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="170" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="171" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="172" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="173" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="174" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="175" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="176" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="177" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="178" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="179" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="180" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="181" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="182" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="183" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="184" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="185" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="186" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="187" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="188" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="189" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="190" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="191" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="192" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="193" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="194" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="195" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="196" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="197" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="198" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="199" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="200" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="201" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="202" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="203" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="204" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="205" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="206" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="207" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="208" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="209" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="210" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="211" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="212" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="213" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="214" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="215" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="216" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="217" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="218" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="219" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="220" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="221" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="222" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="223" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="224" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="225" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="226" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="227" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="228" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="229" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="230" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="231" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="232" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="233" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="234" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="235" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="236" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="237" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="238" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="239" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="240" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="241" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="242" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="243" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="244" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="245" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="246" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="247" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="248" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="249" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="250" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="251" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="252" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="253" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="254" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="255" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="256" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="257" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="258" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="259" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="260" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="261" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="262" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="263" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="264" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="265" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="266" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="267" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="268" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="269" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="270" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="271" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="272" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="273" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="274" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="275" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="276" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="277" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="278" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="279" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="280" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="281" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="282" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="283" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="284" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="285" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="286" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="287" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="288" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="289" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="290" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="291" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="292" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="293" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="294" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="295" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="296" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="297" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="298" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="299" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="300" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="301" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="302" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="303" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="304" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="305" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="306" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="307" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="308" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="309" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="310" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="311" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="312" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="313" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="314" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="315" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="316" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="317" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="318" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="319" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="320" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="321" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="322" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="323" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="324" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="325" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="326" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="327" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="328" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="329" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="330" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="331" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="332" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="333" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="334" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="335" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="336" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="337" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="338" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="339" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="340" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="341" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="342" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="343" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="344" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="345" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="346" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="347" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="348" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="349" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="350" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="351" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="352" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="353" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="354" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="355" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="356" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="357" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="358" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="359" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="360" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="361" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="362" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="363" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="364" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="365" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="366" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="367" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="368" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="369" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="370" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="371" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="372" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="373" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="374" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="375" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="376" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="377" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="378" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="379" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="380" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="381" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="382" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="383" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="384" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="385" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="386" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="387" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="388" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="389" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="390" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="391" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="392" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="393" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="394" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="395" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="396" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="397" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="398" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="399" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="400" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="401" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="402" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="403" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="404" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="405" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="406" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="407" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="408" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="409" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="410" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="411" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="412" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="413" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="414" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="415" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="416" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="417" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="418" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="419" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="420" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="421" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="422" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="423" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="424" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="425" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="426" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="427" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="428" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="429" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="430" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="431" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="432" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="433" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="434" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="435" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="436" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="437" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="438" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="439" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="440" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="441" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="442" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="443" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="444" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="445" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="446" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="447" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="448" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="449" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="450" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="451" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="452" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="453" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="454" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="455" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="456" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="457" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="458" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="459" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="460" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="461" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="462" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="463" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="464" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="465" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="466" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="467" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="468" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="469" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="470" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="471" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="472" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="473" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="474" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="475" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="476" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="477" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="478" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="479" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="480" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="481" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="482" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="483" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="484" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="485" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="486" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="487" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="488" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="489" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="490" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="491" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="492" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="493" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="494" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="495" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="496" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="497" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="498" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="499" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="500" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="501" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="502" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="503" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="504" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="505" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="506" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="507" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="508" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="509" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="510" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="511" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="512" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="513" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="514" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="515" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="516" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="517" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="518" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="519" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="520" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="521" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="522" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="523" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="524" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="525" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="526" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="527" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="528" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="529" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="530" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="531" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="532" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="533" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="534" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="535" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="536" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="537" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="538" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="539" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="540" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="541" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="542" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="543" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="544" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="545" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="546" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="547" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="548" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="549" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="550" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="551" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="552" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="553" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="554" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="555" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="556" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="557" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="558" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="559" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="560" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="561" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="562" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="563" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="564" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="565" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="566" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="567" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="568" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="569" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="570" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="571" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="572" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="573" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="574" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="575" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="576" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="577" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="578" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="579" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="580" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="581" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="582" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="583" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="584" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="585" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="586" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="587" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="588" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="589" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="590" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="591" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="592" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="593" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="594" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="595" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="596" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="597" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="598" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="599" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="600" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="601" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="602" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="603" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="604" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="605" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="606" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="607" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="608" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="609" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="610" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="611" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="612" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="613" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="614" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="615" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="616" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="617" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="618" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="619" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="620" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="621" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="622" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="623" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="624" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="625" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="626" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="627" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="628" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="629" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="630" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="631" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="632" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="633" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="634" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="635" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="636" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="637" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="638" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="639" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="640" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="641" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="642" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="643" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="644" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="645" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="646" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="647" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="648" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="649" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="650" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="651" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="652" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="653" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="654" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="655" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="656" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="657" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="658" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="659" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="660" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="661" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="662" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="663" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="664" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="665" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="666" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="667" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="668" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="669" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="670" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="671" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="672" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="673" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="674" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="675" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="676" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="677" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="678" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="679" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="680" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="681" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="682" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="683" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="684" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="685" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="686" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="687" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="688" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="689" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="690" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="691" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="692" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="693" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="694" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="695" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="696" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="697" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="698" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="699" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="700" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="701" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="702" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="703" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="704" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="705" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="706" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="707" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="708" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="709" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="710" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="711" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="712" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="713" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="714" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="715" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="716" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="717" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="718" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="719" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="720" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="721" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="722" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="723" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="724" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="725" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="726" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="727" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="728" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="729" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="730" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="731" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="732" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="733" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="734" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="735" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="736" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="737" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="738" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="739" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="740" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="741" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="742" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="743" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="744" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="745" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="746" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="747" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="748" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="749" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="750" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="751" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="752" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="753" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="754" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="755" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="756" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="757" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="758" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="759" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="760" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="761" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="762" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="763" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="764" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="765" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="766" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="767" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="768" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="769" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="770" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="771" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="772" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="773" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="774" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="775" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="776" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="777" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="778" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="779" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="780" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="781" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="782" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="783" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="784" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="785" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="786" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="787" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="788" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="789" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="790" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="791" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="792" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="793" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="794" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="795" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="796" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="797" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="798" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="799" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="800" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="801" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="802" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="803" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="804" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="805" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="806" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="807" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="808" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="809" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="810" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="811" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="812" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="813" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="814" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="815" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="816" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="817" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="818" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="819" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="820" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="821" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="822" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="823" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="824" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="825" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="826" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="827" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="828" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="829" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="830" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="831" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="832" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="833" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="834" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="835" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="836" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="837" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="838" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="839" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="840" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="841" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="842" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="843" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="844" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="845" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="846" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="847" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="848" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="849" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="850" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="851" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="852" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="853" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="854" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="855" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="856" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="857" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="858" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="859" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="860" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="861" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="862" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="863" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="864" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="865" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="866" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="867" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="868" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="869" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="870" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="871" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="872" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="873" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="874" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="875" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="876" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="877" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="878" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="879" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="880" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="881" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="882" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="883" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="884" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="885" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="886" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="887" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="888" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="889" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="890" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="891" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="892" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="893" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="894" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="895" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="896" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="897" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="898" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="899" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="900" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="901" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="902" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="903" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="904" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="905" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="906" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="907" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="908" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="909" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="910" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="911" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="912" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="913" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="914" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="915" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="916" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="917" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="918" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="919" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="920" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="921" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="922" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="923" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="924" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="925" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="926" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="927" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="928" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="929" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="930" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="931" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="932" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="933" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="934" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="935" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="936" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="937" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="938" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="939" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="940" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="941" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="942" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="943" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="944" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="945" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="946" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="947" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="948" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="949" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="950" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="951" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="952" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="953" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="954" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="955" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="956" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="957" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="958" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="959" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="960" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="961" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="962" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="963" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="964" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="965" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="966" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="967" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="968" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="969" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="970" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="971" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="972" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="973" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="974" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="975" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="976" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="977" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="978" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="979" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="980" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="981" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="982" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="983" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="984" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="985" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="986" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="987" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="988" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="989" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="990" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="991" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="992" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="993" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="994" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="995" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="996" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="997" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="998" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="999" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="1000" customFormat="1" ht="13.5" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AI Audit_Log_NguyenTuanManh.xlsx
+++ b/AI Audit_Log_NguyenTuanManh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28788" windowHeight="12960" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="9708" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="Week 5" sheetId="6" r:id="rId6"/>
     <sheet name="Week 6" sheetId="7" r:id="rId7"/>
     <sheet name="Week 7" sheetId="8" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="109">
   <si>
     <t>STT</t>
   </si>
@@ -371,6 +372,61 @@
   <si>
     <t>AI giải thích mô hình Container: 1000 kiện → Container → Container lên xe. Xe chỉ scan container, 500 đơn cập nhật trạng thái đồng thời.
 Người học quyết định: FreshConnect có cần Container không? Với quy mô B2B nông sản thì nên gom theo lô Shipment hay Container?</t>
+  </si>
+  <si>
+    <t>Standard Workflow – Quy trình kho đồng nhất</t>
+  </si>
+  <si>
+    <t>"Mỗi kho có quy trình khác nhau không, hay cần chuẩn hóa?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất Standard Workflow áp dụng đồng nhất cho mọi kho:
+Unload → Scan → Sort → Load
+Giúp đào tạo nhân viên nhanh và dễ mở rộng thêm kho mới.
+Người học áp dụng: FreshConnect chuẩn hóa quy trình cho tất cả điểm trung chuyển.</t>
+  </si>
+  <si>
+    <t>Hub &amp; Spoke – Phân tầng vùng</t>
+  </si>
+  <si>
+    <t>"Hệ thống tổ chức mạng lưới vận chuyển giữa nhiều tỉnh thành như thế nào?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất mô hình Hub &amp; Spoke:
+Huyện → Hub tỉnh → Hub miền → Hub quốc gia → Hub miền → Hub tỉnh → Huyện
+Ví dụ: An Khê → Hub Gia Lai → Hub Đà Nẵng → Hub Hà Nội → Long Biên.
+Người học quyết định: FreshConnect cần bao nhiêu tầng Hub? Giai đoạn đầu có thể đơn giản hóa còn 2 tầng không?</t>
+  </si>
+  <si>
+    <t>Routing tự động</t>
+  </si>
+  <si>
+    <t>"Ai quyết định tuyến đường vận chuyển cho mỗi đơn hàng?"</t>
+  </si>
+  <si>
+    <t>AI trả lời: Routing Service tự động quyết định, không phải con người. Thuật toán chọn tuyến ngắn nhất hoặc tối ưu chi phí.
+Người học quyết định: FreshConnect dùng thuật toán đơn giản (Dijkstra) hay tích hợp Google Maps Directions API để tính tuyến tối ưu?</t>
+  </si>
+  <si>
+    <t>Tracking – Đọc Event, không lưu vị trí</t>
+  </si>
+  <si>
+    <t>"Hệ thống tracking của Shopee lưu trữ dữ liệu như thế nào để hiển thị timeline?"</t>
+  </si>
+  <si>
+    <t>AI tiết lộ: Tracking không lưu "đang ở đâu" mà lưu chuỗi Event (Arrived Hub A → Loaded Truck → Out for Delivery). App chỉ đọc event list và render timeline.
+Người học áp dụng: FreshConnect dùng bảng TrackingEvent làm nguồn sự thật duy nhất cho toàn bộ lịch sử đơn hàng.</t>
+  </si>
+  <si>
+    <t>Database Schema – Thiết kế CSDL</t>
+  </si>
+  <si>
+    <t>"Cần thiết kế những bảng dữ liệu nào để quản lý toàn bộ hệ thống logistics?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất 7 bảng cốt lõi: Warehouse, Vehicle, Driver, Package, Container, Shipment, TrackingEvent.
+Bảng quan trọng nhất: TrackingEvent — lưu toàn bộ lịch sử.
+Người học quyết định: FreshConnect cần thêm bảng Product, Order liên kết với Package như thế nào?</t>
   </si>
 </sst>
 </file>
@@ -9191,6 +9247,1103 @@
         <v>93</v>
       </c>
     </row>
+    <row r="7" ht="13.5" customHeight="1"/>
+    <row r="8" ht="13.5" customHeight="1"/>
+    <row r="9" ht="13.5" customHeight="1"/>
+    <row r="10" ht="13.5" customHeight="1"/>
+    <row r="11" ht="13.5" customHeight="1"/>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1"/>
+    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="17" ht="13.5" customHeight="1"/>
+    <row r="18" ht="13.5" customHeight="1"/>
+    <row r="19" ht="13.5" customHeight="1"/>
+    <row r="20" ht="13.5" customHeight="1"/>
+    <row r="21" ht="13.5" customHeight="1"/>
+    <row r="22" ht="13.5" customHeight="1"/>
+    <row r="23" ht="13.5" customHeight="1"/>
+    <row r="24" ht="13.5" customHeight="1"/>
+    <row r="25" ht="13.5" customHeight="1"/>
+    <row r="26" ht="13.5" customHeight="1"/>
+    <row r="27" ht="13.5" customHeight="1"/>
+    <row r="28" ht="13.5" customHeight="1"/>
+    <row r="29" ht="13.5" customHeight="1"/>
+    <row r="30" ht="13.5" customHeight="1"/>
+    <row r="31" ht="13.5" customHeight="1"/>
+    <row r="32" ht="13.5" customHeight="1"/>
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1"/>
+    <row r="35" ht="13.5" customHeight="1"/>
+    <row r="36" ht="13.5" customHeight="1"/>
+    <row r="37" ht="13.5" customHeight="1"/>
+    <row r="38" ht="13.5" customHeight="1"/>
+    <row r="39" ht="13.5" customHeight="1"/>
+    <row r="40" ht="13.5" customHeight="1"/>
+    <row r="41" ht="13.5" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1"/>
+    <row r="43" ht="13.5" customHeight="1"/>
+    <row r="44" ht="13.5" customHeight="1"/>
+    <row r="45" ht="13.5" customHeight="1"/>
+    <row r="46" ht="13.5" customHeight="1"/>
+    <row r="47" ht="13.5" customHeight="1"/>
+    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="49" ht="13.5" customHeight="1"/>
+    <row r="50" ht="13.5" customHeight="1"/>
+    <row r="51" ht="13.5" customHeight="1"/>
+    <row r="52" ht="13.5" customHeight="1"/>
+    <row r="53" ht="13.5" customHeight="1"/>
+    <row r="54" ht="13.5" customHeight="1"/>
+    <row r="55" ht="13.5" customHeight="1"/>
+    <row r="56" ht="13.5" customHeight="1"/>
+    <row r="57" ht="13.5" customHeight="1"/>
+    <row r="58" ht="13.5" customHeight="1"/>
+    <row r="59" ht="13.5" customHeight="1"/>
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="62" ht="13.5" customHeight="1"/>
+    <row r="63" ht="13.5" customHeight="1"/>
+    <row r="64" ht="13.5" customHeight="1"/>
+    <row r="65" ht="13.5" customHeight="1"/>
+    <row r="66" ht="13.5" customHeight="1"/>
+    <row r="67" ht="13.5" customHeight="1"/>
+    <row r="68" ht="13.5" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1"/>
+    <row r="71" ht="13.5" customHeight="1"/>
+    <row r="72" ht="13.5" customHeight="1"/>
+    <row r="73" ht="13.5" customHeight="1"/>
+    <row r="74" ht="13.5" customHeight="1"/>
+    <row r="75" ht="13.5" customHeight="1"/>
+    <row r="76" ht="13.5" customHeight="1"/>
+    <row r="77" ht="13.5" customHeight="1"/>
+    <row r="78" ht="13.5" customHeight="1"/>
+    <row r="79" ht="13.5" customHeight="1"/>
+    <row r="80" ht="13.5" customHeight="1"/>
+    <row r="81" ht="13.5" customHeight="1"/>
+    <row r="82" ht="13.5" customHeight="1"/>
+    <row r="83" ht="13.5" customHeight="1"/>
+    <row r="84" ht="13.5" customHeight="1"/>
+    <row r="85" ht="13.5" customHeight="1"/>
+    <row r="86" ht="13.5" customHeight="1"/>
+    <row r="87" ht="13.5" customHeight="1"/>
+    <row r="88" ht="13.5" customHeight="1"/>
+    <row r="89" ht="13.5" customHeight="1"/>
+    <row r="90" ht="13.5" customHeight="1"/>
+    <row r="91" ht="13.5" customHeight="1"/>
+    <row r="92" ht="13.5" customHeight="1"/>
+    <row r="93" ht="13.5" customHeight="1"/>
+    <row r="94" ht="13.5" customHeight="1"/>
+    <row r="95" ht="13.5" customHeight="1"/>
+    <row r="96" ht="13.5" customHeight="1"/>
+    <row r="97" ht="13.5" customHeight="1"/>
+    <row r="98" ht="13.5" customHeight="1"/>
+    <row r="99" ht="13.5" customHeight="1"/>
+    <row r="100" ht="13.5" customHeight="1"/>
+    <row r="101" ht="13.5" customHeight="1"/>
+    <row r="102" ht="13.5" customHeight="1"/>
+    <row r="103" ht="13.5" customHeight="1"/>
+    <row r="104" ht="13.5" customHeight="1"/>
+    <row r="105" ht="13.5" customHeight="1"/>
+    <row r="106" ht="13.5" customHeight="1"/>
+    <row r="107" ht="13.5" customHeight="1"/>
+    <row r="108" ht="13.5" customHeight="1"/>
+    <row r="109" ht="13.5" customHeight="1"/>
+    <row r="110" ht="13.5" customHeight="1"/>
+    <row r="111" ht="13.5" customHeight="1"/>
+    <row r="112" ht="13.5" customHeight="1"/>
+    <row r="113" ht="13.5" customHeight="1"/>
+    <row r="114" ht="13.5" customHeight="1"/>
+    <row r="115" ht="13.5" customHeight="1"/>
+    <row r="116" ht="13.5" customHeight="1"/>
+    <row r="117" ht="13.5" customHeight="1"/>
+    <row r="118" ht="13.5" customHeight="1"/>
+    <row r="119" ht="13.5" customHeight="1"/>
+    <row r="120" ht="13.5" customHeight="1"/>
+    <row r="121" ht="13.5" customHeight="1"/>
+    <row r="122" ht="13.5" customHeight="1"/>
+    <row r="123" ht="13.5" customHeight="1"/>
+    <row r="124" ht="13.5" customHeight="1"/>
+    <row r="125" ht="13.5" customHeight="1"/>
+    <row r="126" ht="13.5" customHeight="1"/>
+    <row r="127" ht="13.5" customHeight="1"/>
+    <row r="128" ht="13.5" customHeight="1"/>
+    <row r="129" ht="13.5" customHeight="1"/>
+    <row r="130" ht="13.5" customHeight="1"/>
+    <row r="131" ht="13.5" customHeight="1"/>
+    <row r="132" ht="13.5" customHeight="1"/>
+    <row r="133" ht="13.5" customHeight="1"/>
+    <row r="134" ht="13.5" customHeight="1"/>
+    <row r="135" ht="13.5" customHeight="1"/>
+    <row r="136" ht="13.5" customHeight="1"/>
+    <row r="137" ht="13.5" customHeight="1"/>
+    <row r="138" ht="13.5" customHeight="1"/>
+    <row r="139" ht="13.5" customHeight="1"/>
+    <row r="140" ht="13.5" customHeight="1"/>
+    <row r="141" ht="13.5" customHeight="1"/>
+    <row r="142" ht="13.5" customHeight="1"/>
+    <row r="143" ht="13.5" customHeight="1"/>
+    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="145" ht="13.5" customHeight="1"/>
+    <row r="146" ht="13.5" customHeight="1"/>
+    <row r="147" ht="13.5" customHeight="1"/>
+    <row r="148" ht="13.5" customHeight="1"/>
+    <row r="149" ht="13.5" customHeight="1"/>
+    <row r="150" ht="13.5" customHeight="1"/>
+    <row r="151" ht="13.5" customHeight="1"/>
+    <row r="152" ht="13.5" customHeight="1"/>
+    <row r="153" ht="13.5" customHeight="1"/>
+    <row r="154" ht="13.5" customHeight="1"/>
+    <row r="155" ht="13.5" customHeight="1"/>
+    <row r="156" ht="13.5" customHeight="1"/>
+    <row r="157" ht="13.5" customHeight="1"/>
+    <row r="158" ht="13.5" customHeight="1"/>
+    <row r="159" ht="13.5" customHeight="1"/>
+    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="161" ht="13.5" customHeight="1"/>
+    <row r="162" ht="13.5" customHeight="1"/>
+    <row r="163" ht="13.5" customHeight="1"/>
+    <row r="164" ht="13.5" customHeight="1"/>
+    <row r="165" ht="13.5" customHeight="1"/>
+    <row r="166" ht="13.5" customHeight="1"/>
+    <row r="167" ht="13.5" customHeight="1"/>
+    <row r="168" ht="13.5" customHeight="1"/>
+    <row r="169" ht="13.5" customHeight="1"/>
+    <row r="170" ht="13.5" customHeight="1"/>
+    <row r="171" ht="13.5" customHeight="1"/>
+    <row r="172" ht="13.5" customHeight="1"/>
+    <row r="173" ht="13.5" customHeight="1"/>
+    <row r="174" ht="13.5" customHeight="1"/>
+    <row r="175" ht="13.5" customHeight="1"/>
+    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="177" ht="13.5" customHeight="1"/>
+    <row r="178" ht="13.5" customHeight="1"/>
+    <row r="179" ht="13.5" customHeight="1"/>
+    <row r="180" ht="13.5" customHeight="1"/>
+    <row r="181" ht="13.5" customHeight="1"/>
+    <row r="182" ht="13.5" customHeight="1"/>
+    <row r="183" ht="13.5" customHeight="1"/>
+    <row r="184" ht="13.5" customHeight="1"/>
+    <row r="185" ht="13.5" customHeight="1"/>
+    <row r="186" ht="13.5" customHeight="1"/>
+    <row r="187" ht="13.5" customHeight="1"/>
+    <row r="188" ht="13.5" customHeight="1"/>
+    <row r="189" ht="13.5" customHeight="1"/>
+    <row r="190" ht="13.5" customHeight="1"/>
+    <row r="191" ht="13.5" customHeight="1"/>
+    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" ht="13.5" customHeight="1"/>
+    <row r="210" ht="13.5" customHeight="1"/>
+    <row r="211" ht="13.5" customHeight="1"/>
+    <row r="212" ht="13.5" customHeight="1"/>
+    <row r="213" ht="13.5" customHeight="1"/>
+    <row r="214" ht="13.5" customHeight="1"/>
+    <row r="215" ht="13.5" customHeight="1"/>
+    <row r="216" ht="13.5" customHeight="1"/>
+    <row r="217" ht="13.5" customHeight="1"/>
+    <row r="218" ht="13.5" customHeight="1"/>
+    <row r="219" ht="13.5" customHeight="1"/>
+    <row r="220" ht="13.5" customHeight="1"/>
+    <row r="221" ht="13.5" customHeight="1"/>
+    <row r="222" ht="13.5" customHeight="1"/>
+    <row r="223" ht="13.5" customHeight="1"/>
+    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="225" ht="13.5" customHeight="1"/>
+    <row r="226" ht="13.5" customHeight="1"/>
+    <row r="227" ht="13.5" customHeight="1"/>
+    <row r="228" ht="13.5" customHeight="1"/>
+    <row r="229" ht="13.5" customHeight="1"/>
+    <row r="230" ht="13.5" customHeight="1"/>
+    <row r="231" ht="13.5" customHeight="1"/>
+    <row r="232" ht="13.5" customHeight="1"/>
+    <row r="233" ht="13.5" customHeight="1"/>
+    <row r="234" ht="13.5" customHeight="1"/>
+    <row r="235" ht="13.5" customHeight="1"/>
+    <row r="236" ht="13.5" customHeight="1"/>
+    <row r="237" ht="13.5" customHeight="1"/>
+    <row r="238" ht="13.5" customHeight="1"/>
+    <row r="239" ht="13.5" customHeight="1"/>
+    <row r="240" ht="13.5" customHeight="1"/>
+    <row r="241" ht="13.5" customHeight="1"/>
+    <row r="242" ht="13.5" customHeight="1"/>
+    <row r="243" ht="13.5" customHeight="1"/>
+    <row r="244" ht="13.5" customHeight="1"/>
+    <row r="245" ht="13.5" customHeight="1"/>
+    <row r="246" ht="13.5" customHeight="1"/>
+    <row r="247" ht="13.5" customHeight="1"/>
+    <row r="248" ht="13.5" customHeight="1"/>
+    <row r="249" ht="13.5" customHeight="1"/>
+    <row r="250" ht="13.5" customHeight="1"/>
+    <row r="251" ht="13.5" customHeight="1"/>
+    <row r="252" ht="13.5" customHeight="1"/>
+    <row r="253" ht="13.5" customHeight="1"/>
+    <row r="254" ht="13.5" customHeight="1"/>
+    <row r="255" ht="13.5" customHeight="1"/>
+    <row r="256" ht="13.5" customHeight="1"/>
+    <row r="257" ht="13.5" customHeight="1"/>
+    <row r="258" ht="13.5" customHeight="1"/>
+    <row r="259" ht="13.5" customHeight="1"/>
+    <row r="260" ht="13.5" customHeight="1"/>
+    <row r="261" ht="13.5" customHeight="1"/>
+    <row r="262" ht="13.5" customHeight="1"/>
+    <row r="263" ht="13.5" customHeight="1"/>
+    <row r="264" ht="13.5" customHeight="1"/>
+    <row r="265" ht="13.5" customHeight="1"/>
+    <row r="266" ht="13.5" customHeight="1"/>
+    <row r="267" ht="13.5" customHeight="1"/>
+    <row r="268" ht="13.5" customHeight="1"/>
+    <row r="269" ht="13.5" customHeight="1"/>
+    <row r="270" ht="13.5" customHeight="1"/>
+    <row r="271" ht="13.5" customHeight="1"/>
+    <row r="272" ht="13.5" customHeight="1"/>
+    <row r="273" ht="13.5" customHeight="1"/>
+    <row r="274" ht="13.5" customHeight="1"/>
+    <row r="275" ht="13.5" customHeight="1"/>
+    <row r="276" ht="13.5" customHeight="1"/>
+    <row r="277" ht="13.5" customHeight="1"/>
+    <row r="278" ht="13.5" customHeight="1"/>
+    <row r="279" ht="13.5" customHeight="1"/>
+    <row r="280" ht="13.5" customHeight="1"/>
+    <row r="281" ht="13.5" customHeight="1"/>
+    <row r="282" ht="13.5" customHeight="1"/>
+    <row r="283" ht="13.5" customHeight="1"/>
+    <row r="284" ht="13.5" customHeight="1"/>
+    <row r="285" ht="13.5" customHeight="1"/>
+    <row r="286" ht="13.5" customHeight="1"/>
+    <row r="287" ht="13.5" customHeight="1"/>
+    <row r="288" ht="13.5" customHeight="1"/>
+    <row r="289" ht="13.5" customHeight="1"/>
+    <row r="290" ht="13.5" customHeight="1"/>
+    <row r="291" ht="13.5" customHeight="1"/>
+    <row r="292" ht="13.5" customHeight="1"/>
+    <row r="293" ht="13.5" customHeight="1"/>
+    <row r="294" ht="13.5" customHeight="1"/>
+    <row r="295" ht="13.5" customHeight="1"/>
+    <row r="296" ht="13.5" customHeight="1"/>
+    <row r="297" ht="13.5" customHeight="1"/>
+    <row r="298" ht="13.5" customHeight="1"/>
+    <row r="299" ht="13.5" customHeight="1"/>
+    <row r="300" ht="13.5" customHeight="1"/>
+    <row r="301" ht="13.5" customHeight="1"/>
+    <row r="302" ht="13.5" customHeight="1"/>
+    <row r="303" ht="13.5" customHeight="1"/>
+    <row r="304" ht="13.5" customHeight="1"/>
+    <row r="305" ht="13.5" customHeight="1"/>
+    <row r="306" ht="13.5" customHeight="1"/>
+    <row r="307" ht="13.5" customHeight="1"/>
+    <row r="308" ht="13.5" customHeight="1"/>
+    <row r="309" ht="13.5" customHeight="1"/>
+    <row r="310" ht="13.5" customHeight="1"/>
+    <row r="311" ht="13.5" customHeight="1"/>
+    <row r="312" ht="13.5" customHeight="1"/>
+    <row r="313" ht="13.5" customHeight="1"/>
+    <row r="314" ht="13.5" customHeight="1"/>
+    <row r="315" ht="13.5" customHeight="1"/>
+    <row r="316" ht="13.5" customHeight="1"/>
+    <row r="317" ht="13.5" customHeight="1"/>
+    <row r="318" ht="13.5" customHeight="1"/>
+    <row r="319" ht="13.5" customHeight="1"/>
+    <row r="320" ht="13.5" customHeight="1"/>
+    <row r="321" ht="13.5" customHeight="1"/>
+    <row r="322" ht="13.5" customHeight="1"/>
+    <row r="323" ht="13.5" customHeight="1"/>
+    <row r="324" ht="13.5" customHeight="1"/>
+    <row r="325" ht="13.5" customHeight="1"/>
+    <row r="326" ht="13.5" customHeight="1"/>
+    <row r="327" ht="13.5" customHeight="1"/>
+    <row r="328" ht="13.5" customHeight="1"/>
+    <row r="329" ht="13.5" customHeight="1"/>
+    <row r="330" ht="13.5" customHeight="1"/>
+    <row r="331" ht="13.5" customHeight="1"/>
+    <row r="332" ht="13.5" customHeight="1"/>
+    <row r="333" ht="13.5" customHeight="1"/>
+    <row r="334" ht="13.5" customHeight="1"/>
+    <row r="335" ht="13.5" customHeight="1"/>
+    <row r="336" ht="13.5" customHeight="1"/>
+    <row r="337" ht="13.5" customHeight="1"/>
+    <row r="338" ht="13.5" customHeight="1"/>
+    <row r="339" ht="13.5" customHeight="1"/>
+    <row r="340" ht="13.5" customHeight="1"/>
+    <row r="341" ht="13.5" customHeight="1"/>
+    <row r="342" ht="13.5" customHeight="1"/>
+    <row r="343" ht="13.5" customHeight="1"/>
+    <row r="344" ht="13.5" customHeight="1"/>
+    <row r="345" ht="13.5" customHeight="1"/>
+    <row r="346" ht="13.5" customHeight="1"/>
+    <row r="347" ht="13.5" customHeight="1"/>
+    <row r="348" ht="13.5" customHeight="1"/>
+    <row r="349" ht="13.5" customHeight="1"/>
+    <row r="350" ht="13.5" customHeight="1"/>
+    <row r="351" ht="13.5" customHeight="1"/>
+    <row r="352" ht="13.5" customHeight="1"/>
+    <row r="353" ht="13.5" customHeight="1"/>
+    <row r="354" ht="13.5" customHeight="1"/>
+    <row r="355" ht="13.5" customHeight="1"/>
+    <row r="356" ht="13.5" customHeight="1"/>
+    <row r="357" ht="13.5" customHeight="1"/>
+    <row r="358" ht="13.5" customHeight="1"/>
+    <row r="359" ht="13.5" customHeight="1"/>
+    <row r="360" ht="13.5" customHeight="1"/>
+    <row r="361" ht="13.5" customHeight="1"/>
+    <row r="362" ht="13.5" customHeight="1"/>
+    <row r="363" ht="13.5" customHeight="1"/>
+    <row r="364" ht="13.5" customHeight="1"/>
+    <row r="365" ht="13.5" customHeight="1"/>
+    <row r="366" ht="13.5" customHeight="1"/>
+    <row r="367" ht="13.5" customHeight="1"/>
+    <row r="368" ht="13.5" customHeight="1"/>
+    <row r="369" ht="13.5" customHeight="1"/>
+    <row r="370" ht="13.5" customHeight="1"/>
+    <row r="371" ht="13.5" customHeight="1"/>
+    <row r="372" ht="13.5" customHeight="1"/>
+    <row r="373" ht="13.5" customHeight="1"/>
+    <row r="374" ht="13.5" customHeight="1"/>
+    <row r="375" ht="13.5" customHeight="1"/>
+    <row r="376" ht="13.5" customHeight="1"/>
+    <row r="377" ht="13.5" customHeight="1"/>
+    <row r="378" ht="13.5" customHeight="1"/>
+    <row r="379" ht="13.5" customHeight="1"/>
+    <row r="380" ht="13.5" customHeight="1"/>
+    <row r="381" ht="13.5" customHeight="1"/>
+    <row r="382" ht="13.5" customHeight="1"/>
+    <row r="383" ht="13.5" customHeight="1"/>
+    <row r="384" ht="13.5" customHeight="1"/>
+    <row r="385" ht="13.5" customHeight="1"/>
+    <row r="386" ht="13.5" customHeight="1"/>
+    <row r="387" ht="13.5" customHeight="1"/>
+    <row r="388" ht="13.5" customHeight="1"/>
+    <row r="389" ht="13.5" customHeight="1"/>
+    <row r="390" ht="13.5" customHeight="1"/>
+    <row r="391" ht="13.5" customHeight="1"/>
+    <row r="392" ht="13.5" customHeight="1"/>
+    <row r="393" ht="13.5" customHeight="1"/>
+    <row r="394" ht="13.5" customHeight="1"/>
+    <row r="395" ht="13.5" customHeight="1"/>
+    <row r="396" ht="13.5" customHeight="1"/>
+    <row r="397" ht="13.5" customHeight="1"/>
+    <row r="398" ht="13.5" customHeight="1"/>
+    <row r="399" ht="13.5" customHeight="1"/>
+    <row r="400" ht="13.5" customHeight="1"/>
+    <row r="401" ht="13.5" customHeight="1"/>
+    <row r="402" ht="13.5" customHeight="1"/>
+    <row r="403" ht="13.5" customHeight="1"/>
+    <row r="404" ht="13.5" customHeight="1"/>
+    <row r="405" ht="13.5" customHeight="1"/>
+    <row r="406" ht="13.5" customHeight="1"/>
+    <row r="407" ht="13.5" customHeight="1"/>
+    <row r="408" ht="13.5" customHeight="1"/>
+    <row r="409" ht="13.5" customHeight="1"/>
+    <row r="410" ht="13.5" customHeight="1"/>
+    <row r="411" ht="13.5" customHeight="1"/>
+    <row r="412" ht="13.5" customHeight="1"/>
+    <row r="413" ht="13.5" customHeight="1"/>
+    <row r="414" ht="13.5" customHeight="1"/>
+    <row r="415" ht="13.5" customHeight="1"/>
+    <row r="416" ht="13.5" customHeight="1"/>
+    <row r="417" ht="13.5" customHeight="1"/>
+    <row r="418" ht="13.5" customHeight="1"/>
+    <row r="419" ht="13.5" customHeight="1"/>
+    <row r="420" ht="13.5" customHeight="1"/>
+    <row r="421" ht="13.5" customHeight="1"/>
+    <row r="422" ht="13.5" customHeight="1"/>
+    <row r="423" ht="13.5" customHeight="1"/>
+    <row r="424" ht="13.5" customHeight="1"/>
+    <row r="425" ht="13.5" customHeight="1"/>
+    <row r="426" ht="13.5" customHeight="1"/>
+    <row r="427" ht="13.5" customHeight="1"/>
+    <row r="428" ht="13.5" customHeight="1"/>
+    <row r="429" ht="13.5" customHeight="1"/>
+    <row r="430" ht="13.5" customHeight="1"/>
+    <row r="431" ht="13.5" customHeight="1"/>
+    <row r="432" ht="13.5" customHeight="1"/>
+    <row r="433" ht="13.5" customHeight="1"/>
+    <row r="434" ht="13.5" customHeight="1"/>
+    <row r="435" ht="13.5" customHeight="1"/>
+    <row r="436" ht="13.5" customHeight="1"/>
+    <row r="437" ht="13.5" customHeight="1"/>
+    <row r="438" ht="13.5" customHeight="1"/>
+    <row r="439" ht="13.5" customHeight="1"/>
+    <row r="440" ht="13.5" customHeight="1"/>
+    <row r="441" ht="13.5" customHeight="1"/>
+    <row r="442" ht="13.5" customHeight="1"/>
+    <row r="443" ht="13.5" customHeight="1"/>
+    <row r="444" ht="13.5" customHeight="1"/>
+    <row r="445" ht="13.5" customHeight="1"/>
+    <row r="446" ht="13.5" customHeight="1"/>
+    <row r="447" ht="13.5" customHeight="1"/>
+    <row r="448" ht="13.5" customHeight="1"/>
+    <row r="449" ht="13.5" customHeight="1"/>
+    <row r="450" ht="13.5" customHeight="1"/>
+    <row r="451" ht="13.5" customHeight="1"/>
+    <row r="452" ht="13.5" customHeight="1"/>
+    <row r="453" ht="13.5" customHeight="1"/>
+    <row r="454" ht="13.5" customHeight="1"/>
+    <row r="455" ht="13.5" customHeight="1"/>
+    <row r="456" ht="13.5" customHeight="1"/>
+    <row r="457" ht="13.5" customHeight="1"/>
+    <row r="458" ht="13.5" customHeight="1"/>
+    <row r="459" ht="13.5" customHeight="1"/>
+    <row r="460" ht="13.5" customHeight="1"/>
+    <row r="461" ht="13.5" customHeight="1"/>
+    <row r="462" ht="13.5" customHeight="1"/>
+    <row r="463" ht="13.5" customHeight="1"/>
+    <row r="464" ht="13.5" customHeight="1"/>
+    <row r="465" ht="13.5" customHeight="1"/>
+    <row r="466" ht="13.5" customHeight="1"/>
+    <row r="467" ht="13.5" customHeight="1"/>
+    <row r="468" ht="13.5" customHeight="1"/>
+    <row r="469" ht="13.5" customHeight="1"/>
+    <row r="470" ht="13.5" customHeight="1"/>
+    <row r="471" ht="13.5" customHeight="1"/>
+    <row r="472" ht="13.5" customHeight="1"/>
+    <row r="473" ht="13.5" customHeight="1"/>
+    <row r="474" ht="13.5" customHeight="1"/>
+    <row r="475" ht="13.5" customHeight="1"/>
+    <row r="476" ht="13.5" customHeight="1"/>
+    <row r="477" ht="13.5" customHeight="1"/>
+    <row r="478" ht="13.5" customHeight="1"/>
+    <row r="479" ht="13.5" customHeight="1"/>
+    <row r="480" ht="13.5" customHeight="1"/>
+    <row r="481" ht="13.5" customHeight="1"/>
+    <row r="482" ht="13.5" customHeight="1"/>
+    <row r="483" ht="13.5" customHeight="1"/>
+    <row r="484" ht="13.5" customHeight="1"/>
+    <row r="485" ht="13.5" customHeight="1"/>
+    <row r="486" ht="13.5" customHeight="1"/>
+    <row r="487" ht="13.5" customHeight="1"/>
+    <row r="488" ht="13.5" customHeight="1"/>
+    <row r="489" ht="13.5" customHeight="1"/>
+    <row r="490" ht="13.5" customHeight="1"/>
+    <row r="491" ht="13.5" customHeight="1"/>
+    <row r="492" ht="13.5" customHeight="1"/>
+    <row r="493" ht="13.5" customHeight="1"/>
+    <row r="494" ht="13.5" customHeight="1"/>
+    <row r="495" ht="13.5" customHeight="1"/>
+    <row r="496" ht="13.5" customHeight="1"/>
+    <row r="497" ht="13.5" customHeight="1"/>
+    <row r="498" ht="13.5" customHeight="1"/>
+    <row r="499" ht="13.5" customHeight="1"/>
+    <row r="500" ht="13.5" customHeight="1"/>
+    <row r="501" ht="13.5" customHeight="1"/>
+    <row r="502" ht="13.5" customHeight="1"/>
+    <row r="503" ht="13.5" customHeight="1"/>
+    <row r="504" ht="13.5" customHeight="1"/>
+    <row r="505" ht="13.5" customHeight="1"/>
+    <row r="506" ht="13.5" customHeight="1"/>
+    <row r="507" ht="13.5" customHeight="1"/>
+    <row r="508" ht="13.5" customHeight="1"/>
+    <row r="509" ht="13.5" customHeight="1"/>
+    <row r="510" ht="13.5" customHeight="1"/>
+    <row r="511" ht="13.5" customHeight="1"/>
+    <row r="512" ht="13.5" customHeight="1"/>
+    <row r="513" ht="13.5" customHeight="1"/>
+    <row r="514" ht="13.5" customHeight="1"/>
+    <row r="515" ht="13.5" customHeight="1"/>
+    <row r="516" ht="13.5" customHeight="1"/>
+    <row r="517" ht="13.5" customHeight="1"/>
+    <row r="518" ht="13.5" customHeight="1"/>
+    <row r="519" ht="13.5" customHeight="1"/>
+    <row r="520" ht="13.5" customHeight="1"/>
+    <row r="521" ht="13.5" customHeight="1"/>
+    <row r="522" ht="13.5" customHeight="1"/>
+    <row r="523" ht="13.5" customHeight="1"/>
+    <row r="524" ht="13.5" customHeight="1"/>
+    <row r="525" ht="13.5" customHeight="1"/>
+    <row r="526" ht="13.5" customHeight="1"/>
+    <row r="527" ht="13.5" customHeight="1"/>
+    <row r="528" ht="13.5" customHeight="1"/>
+    <row r="529" ht="13.5" customHeight="1"/>
+    <row r="530" ht="13.5" customHeight="1"/>
+    <row r="531" ht="13.5" customHeight="1"/>
+    <row r="532" ht="13.5" customHeight="1"/>
+    <row r="533" ht="13.5" customHeight="1"/>
+    <row r="534" ht="13.5" customHeight="1"/>
+    <row r="535" ht="13.5" customHeight="1"/>
+    <row r="536" ht="13.5" customHeight="1"/>
+    <row r="537" ht="13.5" customHeight="1"/>
+    <row r="538" ht="13.5" customHeight="1"/>
+    <row r="539" ht="13.5" customHeight="1"/>
+    <row r="540" ht="13.5" customHeight="1"/>
+    <row r="541" ht="13.5" customHeight="1"/>
+    <row r="542" ht="13.5" customHeight="1"/>
+    <row r="543" ht="13.5" customHeight="1"/>
+    <row r="544" ht="13.5" customHeight="1"/>
+    <row r="545" ht="13.5" customHeight="1"/>
+    <row r="546" ht="13.5" customHeight="1"/>
+    <row r="547" ht="13.5" customHeight="1"/>
+    <row r="548" ht="13.5" customHeight="1"/>
+    <row r="549" ht="13.5" customHeight="1"/>
+    <row r="550" ht="13.5" customHeight="1"/>
+    <row r="551" ht="13.5" customHeight="1"/>
+    <row r="552" ht="13.5" customHeight="1"/>
+    <row r="553" ht="13.5" customHeight="1"/>
+    <row r="554" ht="13.5" customHeight="1"/>
+    <row r="555" ht="13.5" customHeight="1"/>
+    <row r="556" ht="13.5" customHeight="1"/>
+    <row r="557" ht="13.5" customHeight="1"/>
+    <row r="558" ht="13.5" customHeight="1"/>
+    <row r="559" ht="13.5" customHeight="1"/>
+    <row r="560" ht="13.5" customHeight="1"/>
+    <row r="561" ht="13.5" customHeight="1"/>
+    <row r="562" ht="13.5" customHeight="1"/>
+    <row r="563" ht="13.5" customHeight="1"/>
+    <row r="564" ht="13.5" customHeight="1"/>
+    <row r="565" ht="13.5" customHeight="1"/>
+    <row r="566" ht="13.5" customHeight="1"/>
+    <row r="567" ht="13.5" customHeight="1"/>
+    <row r="568" ht="13.5" customHeight="1"/>
+    <row r="569" ht="13.5" customHeight="1"/>
+    <row r="570" ht="13.5" customHeight="1"/>
+    <row r="571" ht="13.5" customHeight="1"/>
+    <row r="572" ht="13.5" customHeight="1"/>
+    <row r="573" ht="13.5" customHeight="1"/>
+    <row r="574" ht="13.5" customHeight="1"/>
+    <row r="575" ht="13.5" customHeight="1"/>
+    <row r="576" ht="13.5" customHeight="1"/>
+    <row r="577" ht="13.5" customHeight="1"/>
+    <row r="578" ht="13.5" customHeight="1"/>
+    <row r="579" ht="13.5" customHeight="1"/>
+    <row r="580" ht="13.5" customHeight="1"/>
+    <row r="581" ht="13.5" customHeight="1"/>
+    <row r="582" ht="13.5" customHeight="1"/>
+    <row r="583" ht="13.5" customHeight="1"/>
+    <row r="584" ht="13.5" customHeight="1"/>
+    <row r="585" ht="13.5" customHeight="1"/>
+    <row r="586" ht="13.5" customHeight="1"/>
+    <row r="587" ht="13.5" customHeight="1"/>
+    <row r="588" ht="13.5" customHeight="1"/>
+    <row r="589" ht="13.5" customHeight="1"/>
+    <row r="590" ht="13.5" customHeight="1"/>
+    <row r="591" ht="13.5" customHeight="1"/>
+    <row r="592" ht="13.5" customHeight="1"/>
+    <row r="593" ht="13.5" customHeight="1"/>
+    <row r="594" ht="13.5" customHeight="1"/>
+    <row r="595" ht="13.5" customHeight="1"/>
+    <row r="596" ht="13.5" customHeight="1"/>
+    <row r="597" ht="13.5" customHeight="1"/>
+    <row r="598" ht="13.5" customHeight="1"/>
+    <row r="599" ht="13.5" customHeight="1"/>
+    <row r="600" ht="13.5" customHeight="1"/>
+    <row r="601" ht="13.5" customHeight="1"/>
+    <row r="602" ht="13.5" customHeight="1"/>
+    <row r="603" ht="13.5" customHeight="1"/>
+    <row r="604" ht="13.5" customHeight="1"/>
+    <row r="605" ht="13.5" customHeight="1"/>
+    <row r="606" ht="13.5" customHeight="1"/>
+    <row r="607" ht="13.5" customHeight="1"/>
+    <row r="608" ht="13.5" customHeight="1"/>
+    <row r="609" ht="13.5" customHeight="1"/>
+    <row r="610" ht="13.5" customHeight="1"/>
+    <row r="611" ht="13.5" customHeight="1"/>
+    <row r="612" ht="13.5" customHeight="1"/>
+    <row r="613" ht="13.5" customHeight="1"/>
+    <row r="614" ht="13.5" customHeight="1"/>
+    <row r="615" ht="13.5" customHeight="1"/>
+    <row r="616" ht="13.5" customHeight="1"/>
+    <row r="617" ht="13.5" customHeight="1"/>
+    <row r="618" ht="13.5" customHeight="1"/>
+    <row r="619" ht="13.5" customHeight="1"/>
+    <row r="620" ht="13.5" customHeight="1"/>
+    <row r="621" ht="13.5" customHeight="1"/>
+    <row r="622" ht="13.5" customHeight="1"/>
+    <row r="623" ht="13.5" customHeight="1"/>
+    <row r="624" ht="13.5" customHeight="1"/>
+    <row r="625" ht="13.5" customHeight="1"/>
+    <row r="626" ht="13.5" customHeight="1"/>
+    <row r="627" ht="13.5" customHeight="1"/>
+    <row r="628" ht="13.5" customHeight="1"/>
+    <row r="629" ht="13.5" customHeight="1"/>
+    <row r="630" ht="13.5" customHeight="1"/>
+    <row r="631" ht="13.5" customHeight="1"/>
+    <row r="632" ht="13.5" customHeight="1"/>
+    <row r="633" ht="13.5" customHeight="1"/>
+    <row r="634" ht="13.5" customHeight="1"/>
+    <row r="635" ht="13.5" customHeight="1"/>
+    <row r="636" ht="13.5" customHeight="1"/>
+    <row r="637" ht="13.5" customHeight="1"/>
+    <row r="638" ht="13.5" customHeight="1"/>
+    <row r="639" ht="13.5" customHeight="1"/>
+    <row r="640" ht="13.5" customHeight="1"/>
+    <row r="641" ht="13.5" customHeight="1"/>
+    <row r="642" ht="13.5" customHeight="1"/>
+    <row r="643" ht="13.5" customHeight="1"/>
+    <row r="644" ht="13.5" customHeight="1"/>
+    <row r="645" ht="13.5" customHeight="1"/>
+    <row r="646" ht="13.5" customHeight="1"/>
+    <row r="647" ht="13.5" customHeight="1"/>
+    <row r="648" ht="13.5" customHeight="1"/>
+    <row r="649" ht="13.5" customHeight="1"/>
+    <row r="650" ht="13.5" customHeight="1"/>
+    <row r="651" ht="13.5" customHeight="1"/>
+    <row r="652" ht="13.5" customHeight="1"/>
+    <row r="653" ht="13.5" customHeight="1"/>
+    <row r="654" ht="13.5" customHeight="1"/>
+    <row r="655" ht="13.5" customHeight="1"/>
+    <row r="656" ht="13.5" customHeight="1"/>
+    <row r="657" ht="13.5" customHeight="1"/>
+    <row r="658" ht="13.5" customHeight="1"/>
+    <row r="659" ht="13.5" customHeight="1"/>
+    <row r="660" ht="13.5" customHeight="1"/>
+    <row r="661" ht="13.5" customHeight="1"/>
+    <row r="662" ht="13.5" customHeight="1"/>
+    <row r="663" ht="13.5" customHeight="1"/>
+    <row r="664" ht="13.5" customHeight="1"/>
+    <row r="665" ht="13.5" customHeight="1"/>
+    <row r="666" ht="13.5" customHeight="1"/>
+    <row r="667" ht="13.5" customHeight="1"/>
+    <row r="668" ht="13.5" customHeight="1"/>
+    <row r="669" ht="13.5" customHeight="1"/>
+    <row r="670" ht="13.5" customHeight="1"/>
+    <row r="671" ht="13.5" customHeight="1"/>
+    <row r="672" ht="13.5" customHeight="1"/>
+    <row r="673" ht="13.5" customHeight="1"/>
+    <row r="674" ht="13.5" customHeight="1"/>
+    <row r="675" ht="13.5" customHeight="1"/>
+    <row r="676" ht="13.5" customHeight="1"/>
+    <row r="677" ht="13.5" customHeight="1"/>
+    <row r="678" ht="13.5" customHeight="1"/>
+    <row r="679" ht="13.5" customHeight="1"/>
+    <row r="680" ht="13.5" customHeight="1"/>
+    <row r="681" ht="13.5" customHeight="1"/>
+    <row r="682" ht="13.5" customHeight="1"/>
+    <row r="683" ht="13.5" customHeight="1"/>
+    <row r="684" ht="13.5" customHeight="1"/>
+    <row r="685" ht="13.5" customHeight="1"/>
+    <row r="686" ht="13.5" customHeight="1"/>
+    <row r="687" ht="13.5" customHeight="1"/>
+    <row r="688" ht="13.5" customHeight="1"/>
+    <row r="689" ht="13.5" customHeight="1"/>
+    <row r="690" ht="13.5" customHeight="1"/>
+    <row r="691" ht="13.5" customHeight="1"/>
+    <row r="692" ht="13.5" customHeight="1"/>
+    <row r="693" ht="13.5" customHeight="1"/>
+    <row r="694" ht="13.5" customHeight="1"/>
+    <row r="695" ht="13.5" customHeight="1"/>
+    <row r="696" ht="13.5" customHeight="1"/>
+    <row r="697" ht="13.5" customHeight="1"/>
+    <row r="698" ht="13.5" customHeight="1"/>
+    <row r="699" ht="13.5" customHeight="1"/>
+    <row r="700" ht="13.5" customHeight="1"/>
+    <row r="701" ht="13.5" customHeight="1"/>
+    <row r="702" ht="13.5" customHeight="1"/>
+    <row r="703" ht="13.5" customHeight="1"/>
+    <row r="704" ht="13.5" customHeight="1"/>
+    <row r="705" ht="13.5" customHeight="1"/>
+    <row r="706" ht="13.5" customHeight="1"/>
+    <row r="707" ht="13.5" customHeight="1"/>
+    <row r="708" ht="13.5" customHeight="1"/>
+    <row r="709" ht="13.5" customHeight="1"/>
+    <row r="710" ht="13.5" customHeight="1"/>
+    <row r="711" ht="13.5" customHeight="1"/>
+    <row r="712" ht="13.5" customHeight="1"/>
+    <row r="713" ht="13.5" customHeight="1"/>
+    <row r="714" ht="13.5" customHeight="1"/>
+    <row r="715" ht="13.5" customHeight="1"/>
+    <row r="716" ht="13.5" customHeight="1"/>
+    <row r="717" ht="13.5" customHeight="1"/>
+    <row r="718" ht="13.5" customHeight="1"/>
+    <row r="719" ht="13.5" customHeight="1"/>
+    <row r="720" ht="13.5" customHeight="1"/>
+    <row r="721" ht="13.5" customHeight="1"/>
+    <row r="722" ht="13.5" customHeight="1"/>
+    <row r="723" ht="13.5" customHeight="1"/>
+    <row r="724" ht="13.5" customHeight="1"/>
+    <row r="725" ht="13.5" customHeight="1"/>
+    <row r="726" ht="13.5" customHeight="1"/>
+    <row r="727" ht="13.5" customHeight="1"/>
+    <row r="728" ht="13.5" customHeight="1"/>
+    <row r="729" ht="13.5" customHeight="1"/>
+    <row r="730" ht="13.5" customHeight="1"/>
+    <row r="731" ht="13.5" customHeight="1"/>
+    <row r="732" ht="13.5" customHeight="1"/>
+    <row r="733" ht="13.5" customHeight="1"/>
+    <row r="734" ht="13.5" customHeight="1"/>
+    <row r="735" ht="13.5" customHeight="1"/>
+    <row r="736" ht="13.5" customHeight="1"/>
+    <row r="737" ht="13.5" customHeight="1"/>
+    <row r="738" ht="13.5" customHeight="1"/>
+    <row r="739" ht="13.5" customHeight="1"/>
+    <row r="740" ht="13.5" customHeight="1"/>
+    <row r="741" ht="13.5" customHeight="1"/>
+    <row r="742" ht="13.5" customHeight="1"/>
+    <row r="743" ht="13.5" customHeight="1"/>
+    <row r="744" ht="13.5" customHeight="1"/>
+    <row r="745" ht="13.5" customHeight="1"/>
+    <row r="746" ht="13.5" customHeight="1"/>
+    <row r="747" ht="13.5" customHeight="1"/>
+    <row r="748" ht="13.5" customHeight="1"/>
+    <row r="749" ht="13.5" customHeight="1"/>
+    <row r="750" ht="13.5" customHeight="1"/>
+    <row r="751" ht="13.5" customHeight="1"/>
+    <row r="752" ht="13.5" customHeight="1"/>
+    <row r="753" ht="13.5" customHeight="1"/>
+    <row r="754" ht="13.5" customHeight="1"/>
+    <row r="755" ht="13.5" customHeight="1"/>
+    <row r="756" ht="13.5" customHeight="1"/>
+    <row r="757" ht="13.5" customHeight="1"/>
+    <row r="758" ht="13.5" customHeight="1"/>
+    <row r="759" ht="13.5" customHeight="1"/>
+    <row r="760" ht="13.5" customHeight="1"/>
+    <row r="761" ht="13.5" customHeight="1"/>
+    <row r="762" ht="13.5" customHeight="1"/>
+    <row r="763" ht="13.5" customHeight="1"/>
+    <row r="764" ht="13.5" customHeight="1"/>
+    <row r="765" ht="13.5" customHeight="1"/>
+    <row r="766" ht="13.5" customHeight="1"/>
+    <row r="767" ht="13.5" customHeight="1"/>
+    <row r="768" ht="13.5" customHeight="1"/>
+    <row r="769" ht="13.5" customHeight="1"/>
+    <row r="770" ht="13.5" customHeight="1"/>
+    <row r="771" ht="13.5" customHeight="1"/>
+    <row r="772" ht="13.5" customHeight="1"/>
+    <row r="773" ht="13.5" customHeight="1"/>
+    <row r="774" ht="13.5" customHeight="1"/>
+    <row r="775" ht="13.5" customHeight="1"/>
+    <row r="776" ht="13.5" customHeight="1"/>
+    <row r="777" ht="13.5" customHeight="1"/>
+    <row r="778" ht="13.5" customHeight="1"/>
+    <row r="779" ht="13.5" customHeight="1"/>
+    <row r="780" ht="13.5" customHeight="1"/>
+    <row r="781" ht="13.5" customHeight="1"/>
+    <row r="782" ht="13.5" customHeight="1"/>
+    <row r="783" ht="13.5" customHeight="1"/>
+    <row r="784" ht="13.5" customHeight="1"/>
+    <row r="785" ht="13.5" customHeight="1"/>
+    <row r="786" ht="13.5" customHeight="1"/>
+    <row r="787" ht="13.5" customHeight="1"/>
+    <row r="788" ht="13.5" customHeight="1"/>
+    <row r="789" ht="13.5" customHeight="1"/>
+    <row r="790" ht="13.5" customHeight="1"/>
+    <row r="791" ht="13.5" customHeight="1"/>
+    <row r="792" ht="13.5" customHeight="1"/>
+    <row r="793" ht="13.5" customHeight="1"/>
+    <row r="794" ht="13.5" customHeight="1"/>
+    <row r="795" ht="13.5" customHeight="1"/>
+    <row r="796" ht="13.5" customHeight="1"/>
+    <row r="797" ht="13.5" customHeight="1"/>
+    <row r="798" ht="13.5" customHeight="1"/>
+    <row r="799" ht="13.5" customHeight="1"/>
+    <row r="800" ht="13.5" customHeight="1"/>
+    <row r="801" ht="13.5" customHeight="1"/>
+    <row r="802" ht="13.5" customHeight="1"/>
+    <row r="803" ht="13.5" customHeight="1"/>
+    <row r="804" ht="13.5" customHeight="1"/>
+    <row r="805" ht="13.5" customHeight="1"/>
+    <row r="806" ht="13.5" customHeight="1"/>
+    <row r="807" ht="13.5" customHeight="1"/>
+    <row r="808" ht="13.5" customHeight="1"/>
+    <row r="809" ht="13.5" customHeight="1"/>
+    <row r="810" ht="13.5" customHeight="1"/>
+    <row r="811" ht="13.5" customHeight="1"/>
+    <row r="812" ht="13.5" customHeight="1"/>
+    <row r="813" ht="13.5" customHeight="1"/>
+    <row r="814" ht="13.5" customHeight="1"/>
+    <row r="815" ht="13.5" customHeight="1"/>
+    <row r="816" ht="13.5" customHeight="1"/>
+    <row r="817" ht="13.5" customHeight="1"/>
+    <row r="818" ht="13.5" customHeight="1"/>
+    <row r="819" ht="13.5" customHeight="1"/>
+    <row r="820" ht="13.5" customHeight="1"/>
+    <row r="821" ht="13.5" customHeight="1"/>
+    <row r="822" ht="13.5" customHeight="1"/>
+    <row r="823" ht="13.5" customHeight="1"/>
+    <row r="824" ht="13.5" customHeight="1"/>
+    <row r="825" ht="13.5" customHeight="1"/>
+    <row r="826" ht="13.5" customHeight="1"/>
+    <row r="827" ht="13.5" customHeight="1"/>
+    <row r="828" ht="13.5" customHeight="1"/>
+    <row r="829" ht="13.5" customHeight="1"/>
+    <row r="830" ht="13.5" customHeight="1"/>
+    <row r="831" ht="13.5" customHeight="1"/>
+    <row r="832" ht="13.5" customHeight="1"/>
+    <row r="833" ht="13.5" customHeight="1"/>
+    <row r="834" ht="13.5" customHeight="1"/>
+    <row r="835" ht="13.5" customHeight="1"/>
+    <row r="836" ht="13.5" customHeight="1"/>
+    <row r="837" ht="13.5" customHeight="1"/>
+    <row r="838" ht="13.5" customHeight="1"/>
+    <row r="839" ht="13.5" customHeight="1"/>
+    <row r="840" ht="13.5" customHeight="1"/>
+    <row r="841" ht="13.5" customHeight="1"/>
+    <row r="842" ht="13.5" customHeight="1"/>
+    <row r="843" ht="13.5" customHeight="1"/>
+    <row r="844" ht="13.5" customHeight="1"/>
+    <row r="845" ht="13.5" customHeight="1"/>
+    <row r="846" ht="13.5" customHeight="1"/>
+    <row r="847" ht="13.5" customHeight="1"/>
+    <row r="848" ht="13.5" customHeight="1"/>
+    <row r="849" ht="13.5" customHeight="1"/>
+    <row r="850" ht="13.5" customHeight="1"/>
+    <row r="851" ht="13.5" customHeight="1"/>
+    <row r="852" ht="13.5" customHeight="1"/>
+    <row r="853" ht="13.5" customHeight="1"/>
+    <row r="854" ht="13.5" customHeight="1"/>
+    <row r="855" ht="13.5" customHeight="1"/>
+    <row r="856" ht="13.5" customHeight="1"/>
+    <row r="857" ht="13.5" customHeight="1"/>
+    <row r="858" ht="13.5" customHeight="1"/>
+    <row r="859" ht="13.5" customHeight="1"/>
+    <row r="860" ht="13.5" customHeight="1"/>
+    <row r="861" ht="13.5" customHeight="1"/>
+    <row r="862" ht="13.5" customHeight="1"/>
+    <row r="863" ht="13.5" customHeight="1"/>
+    <row r="864" ht="13.5" customHeight="1"/>
+    <row r="865" ht="13.5" customHeight="1"/>
+    <row r="866" ht="13.5" customHeight="1"/>
+    <row r="867" ht="13.5" customHeight="1"/>
+    <row r="868" ht="13.5" customHeight="1"/>
+    <row r="869" ht="13.5" customHeight="1"/>
+    <row r="870" ht="13.5" customHeight="1"/>
+    <row r="871" ht="13.5" customHeight="1"/>
+    <row r="872" ht="13.5" customHeight="1"/>
+    <row r="873" ht="13.5" customHeight="1"/>
+    <row r="874" ht="13.5" customHeight="1"/>
+    <row r="875" ht="13.5" customHeight="1"/>
+    <row r="876" ht="13.5" customHeight="1"/>
+    <row r="877" ht="13.5" customHeight="1"/>
+    <row r="878" ht="13.5" customHeight="1"/>
+    <row r="879" ht="13.5" customHeight="1"/>
+    <row r="880" ht="13.5" customHeight="1"/>
+    <row r="881" ht="13.5" customHeight="1"/>
+    <row r="882" ht="13.5" customHeight="1"/>
+    <row r="883" ht="13.5" customHeight="1"/>
+    <row r="884" ht="13.5" customHeight="1"/>
+    <row r="885" ht="13.5" customHeight="1"/>
+    <row r="886" ht="13.5" customHeight="1"/>
+    <row r="887" ht="13.5" customHeight="1"/>
+    <row r="888" ht="13.5" customHeight="1"/>
+    <row r="889" ht="13.5" customHeight="1"/>
+    <row r="890" ht="13.5" customHeight="1"/>
+    <row r="891" ht="13.5" customHeight="1"/>
+    <row r="892" ht="13.5" customHeight="1"/>
+    <row r="893" ht="13.5" customHeight="1"/>
+    <row r="894" ht="13.5" customHeight="1"/>
+    <row r="895" ht="13.5" customHeight="1"/>
+    <row r="896" ht="13.5" customHeight="1"/>
+    <row r="897" ht="13.5" customHeight="1"/>
+    <row r="898" ht="13.5" customHeight="1"/>
+    <row r="899" ht="13.5" customHeight="1"/>
+    <row r="900" ht="13.5" customHeight="1"/>
+    <row r="901" ht="13.5" customHeight="1"/>
+    <row r="902" ht="13.5" customHeight="1"/>
+    <row r="903" ht="13.5" customHeight="1"/>
+    <row r="904" ht="13.5" customHeight="1"/>
+    <row r="905" ht="13.5" customHeight="1"/>
+    <row r="906" ht="13.5" customHeight="1"/>
+    <row r="907" ht="13.5" customHeight="1"/>
+    <row r="908" ht="13.5" customHeight="1"/>
+    <row r="909" ht="13.5" customHeight="1"/>
+    <row r="910" ht="13.5" customHeight="1"/>
+    <row r="911" ht="13.5" customHeight="1"/>
+    <row r="912" ht="13.5" customHeight="1"/>
+    <row r="913" ht="13.5" customHeight="1"/>
+    <row r="914" ht="13.5" customHeight="1"/>
+    <row r="915" ht="13.5" customHeight="1"/>
+    <row r="916" ht="13.5" customHeight="1"/>
+    <row r="917" ht="13.5" customHeight="1"/>
+    <row r="918" ht="13.5" customHeight="1"/>
+    <row r="919" ht="13.5" customHeight="1"/>
+    <row r="920" ht="13.5" customHeight="1"/>
+    <row r="921" ht="13.5" customHeight="1"/>
+    <row r="922" ht="13.5" customHeight="1"/>
+    <row r="923" ht="13.5" customHeight="1"/>
+    <row r="924" ht="13.5" customHeight="1"/>
+    <row r="925" ht="13.5" customHeight="1"/>
+    <row r="926" ht="13.5" customHeight="1"/>
+    <row r="927" ht="13.5" customHeight="1"/>
+    <row r="928" ht="13.5" customHeight="1"/>
+    <row r="929" ht="13.5" customHeight="1"/>
+    <row r="930" ht="13.5" customHeight="1"/>
+    <row r="931" ht="13.5" customHeight="1"/>
+    <row r="932" ht="13.5" customHeight="1"/>
+    <row r="933" ht="13.5" customHeight="1"/>
+    <row r="934" ht="13.5" customHeight="1"/>
+    <row r="935" ht="13.5" customHeight="1"/>
+    <row r="936" ht="13.5" customHeight="1"/>
+    <row r="937" ht="13.5" customHeight="1"/>
+    <row r="938" ht="13.5" customHeight="1"/>
+    <row r="939" ht="13.5" customHeight="1"/>
+    <row r="940" ht="13.5" customHeight="1"/>
+    <row r="941" ht="13.5" customHeight="1"/>
+    <row r="942" ht="13.5" customHeight="1"/>
+    <row r="943" ht="13.5" customHeight="1"/>
+    <row r="944" ht="13.5" customHeight="1"/>
+    <row r="945" ht="13.5" customHeight="1"/>
+    <row r="946" ht="13.5" customHeight="1"/>
+    <row r="947" ht="13.5" customHeight="1"/>
+    <row r="948" ht="13.5" customHeight="1"/>
+    <row r="949" ht="13.5" customHeight="1"/>
+    <row r="950" ht="13.5" customHeight="1"/>
+    <row r="951" ht="13.5" customHeight="1"/>
+    <row r="952" ht="13.5" customHeight="1"/>
+    <row r="953" ht="13.5" customHeight="1"/>
+    <row r="954" ht="13.5" customHeight="1"/>
+    <row r="955" ht="13.5" customHeight="1"/>
+    <row r="956" ht="13.5" customHeight="1"/>
+    <row r="957" ht="13.5" customHeight="1"/>
+    <row r="958" ht="13.5" customHeight="1"/>
+    <row r="959" ht="13.5" customHeight="1"/>
+    <row r="960" ht="13.5" customHeight="1"/>
+    <row r="961" ht="13.5" customHeight="1"/>
+    <row r="962" ht="13.5" customHeight="1"/>
+    <row r="963" ht="13.5" customHeight="1"/>
+    <row r="964" ht="13.5" customHeight="1"/>
+    <row r="965" ht="13.5" customHeight="1"/>
+    <row r="966" ht="13.5" customHeight="1"/>
+    <row r="967" ht="13.5" customHeight="1"/>
+    <row r="968" ht="13.5" customHeight="1"/>
+    <row r="969" ht="13.5" customHeight="1"/>
+    <row r="970" ht="13.5" customHeight="1"/>
+    <row r="971" ht="13.5" customHeight="1"/>
+    <row r="972" ht="13.5" customHeight="1"/>
+    <row r="973" ht="13.5" customHeight="1"/>
+    <row r="974" ht="13.5" customHeight="1"/>
+    <row r="975" ht="13.5" customHeight="1"/>
+    <row r="976" ht="13.5" customHeight="1"/>
+    <row r="977" ht="13.5" customHeight="1"/>
+    <row r="978" ht="13.5" customHeight="1"/>
+    <row r="979" ht="13.5" customHeight="1"/>
+    <row r="980" ht="13.5" customHeight="1"/>
+    <row r="981" ht="13.5" customHeight="1"/>
+    <row r="982" ht="13.5" customHeight="1"/>
+    <row r="983" ht="13.5" customHeight="1"/>
+    <row r="984" ht="13.5" customHeight="1"/>
+    <row r="985" ht="13.5" customHeight="1"/>
+    <row r="986" ht="13.5" customHeight="1"/>
+    <row r="987" ht="13.5" customHeight="1"/>
+    <row r="988" ht="13.5" customHeight="1"/>
+    <row r="989" ht="13.5" customHeight="1"/>
+    <row r="990" ht="13.5" customHeight="1"/>
+    <row r="991" ht="13.5" customHeight="1"/>
+    <row r="992" ht="13.5" customHeight="1"/>
+    <row r="993" ht="13.5" customHeight="1"/>
+    <row r="994" ht="13.5" customHeight="1"/>
+    <row r="995" ht="13.5" customHeight="1"/>
+    <row r="996" ht="13.5" customHeight="1"/>
+    <row r="997" ht="13.5" customHeight="1"/>
+    <row r="998" ht="13.5" customHeight="1"/>
+    <row r="999" ht="13.5" customHeight="1"/>
+    <row r="1000" ht="13.5" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8833333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="26" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="110.4" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="124.2" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="96.6" spans="1:4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" customFormat="1" ht="13.5" customHeight="1"/>
     <row r="8" customFormat="1" ht="13.5" customHeight="1"/>
     <row r="9" customFormat="1" ht="13.5" customHeight="1"/>
